--- a/research/traditional_assets/database/data/jordan/jordan_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0142</v>
+        <v>0.03435</v>
       </c>
       <c r="E2">
-        <v>-0.04190000000000001</v>
+        <v>0.05125</v>
       </c>
       <c r="G2">
-        <v>0.07630427231677667</v>
+        <v>0.08903522607781283</v>
       </c>
       <c r="H2">
-        <v>0.07630427231677667</v>
+        <v>0.08903522607781283</v>
       </c>
       <c r="I2">
-        <v>0.06803403959708232</v>
+        <v>0.07562828601472135</v>
       </c>
       <c r="J2">
-        <v>0.05632248712854433</v>
+        <v>0.06352201954263204</v>
       </c>
       <c r="K2">
-        <v>14.279</v>
+        <v>20.821</v>
       </c>
       <c r="L2">
-        <v>0.04959708232025009</v>
+        <v>0.05473449001051525</v>
       </c>
       <c r="M2">
-        <v>8.318999999999999</v>
+        <v>15.737</v>
       </c>
       <c r="N2">
-        <v>0.03511311835218638</v>
+        <v>0.0523589299973383</v>
       </c>
       <c r="O2">
-        <v>0.5826038237971846</v>
+        <v>0.7558234474809087</v>
       </c>
       <c r="P2">
-        <v>8.318999999999999</v>
+        <v>15.737</v>
       </c>
       <c r="Q2">
-        <v>0.03511311835218638</v>
+        <v>0.0523589299973383</v>
       </c>
       <c r="R2">
-        <v>0.5826038237971846</v>
+        <v>0.7558234474809087</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>83.84</v>
+        <v>112.755</v>
       </c>
       <c r="V2">
-        <v>0.3538747256457876</v>
+        <v>0.3751497205216928</v>
       </c>
       <c r="W2">
-        <v>0.05</v>
+        <v>0.06898734177215191</v>
       </c>
       <c r="X2">
-        <v>0.07577902151990337</v>
+        <v>0.1225413288938654</v>
       </c>
       <c r="Y2">
-        <v>-0.02577902151990337</v>
+        <v>-0.05355398712171354</v>
       </c>
       <c r="Z2">
-        <v>1.614848302978971</v>
+        <v>1.234455723149614</v>
       </c>
       <c r="AA2">
-        <v>0.07325984597836493</v>
+        <v>0.08238851095993954</v>
       </c>
       <c r="AB2">
-        <v>0.07577902151990337</v>
+        <v>0.1225413288938654</v>
       </c>
       <c r="AC2">
-        <v>-0.009934471896354644</v>
+        <v>-0.04179864585805221</v>
       </c>
       <c r="AD2">
-        <v>28.113</v>
+        <v>20.134</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>28.113</v>
+        <v>20.134</v>
       </c>
       <c r="AG2">
-        <v>-55.727</v>
+        <v>-92.621</v>
       </c>
       <c r="AH2">
-        <v>0.1060735832896281</v>
+        <v>0.06278259025737931</v>
       </c>
       <c r="AI2">
-        <v>0.08785779244522365</v>
+        <v>0.05356012279404332</v>
       </c>
       <c r="AJ2">
-        <v>-0.3075560314140171</v>
+        <v>-0.4454238983548059</v>
       </c>
       <c r="AK2">
-        <v>-0.2359883629834465</v>
+        <v>-0.3519583217750485</v>
       </c>
       <c r="AL2">
-        <v>1.365</v>
+        <v>2.119</v>
       </c>
       <c r="AM2">
-        <v>1.362</v>
+        <v>2.119</v>
       </c>
       <c r="AN2">
-        <v>1.237912813738441</v>
+        <v>0.6200609774876042</v>
       </c>
       <c r="AO2">
-        <v>14.34945054945055</v>
+        <v>13.57668711656442</v>
       </c>
       <c r="AP2">
-        <v>-2.453852928225452</v>
+        <v>-2.852422161313172</v>
       </c>
       <c r="AQ2">
-        <v>14.38105726872246</v>
+        <v>13.57668711656442</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0696</v>
+        <v>0.0761</v>
       </c>
       <c r="E3">
-        <v>0.0458</v>
+        <v>0.0398</v>
       </c>
       <c r="G3">
-        <v>0.138876404494382</v>
+        <v>0.1219148936170213</v>
       </c>
       <c r="H3">
-        <v>0.138876404494382</v>
+        <v>0.1219148936170213</v>
       </c>
       <c r="I3">
-        <v>0.1274157303370786</v>
+        <v>0.09659574468085107</v>
       </c>
       <c r="J3">
-        <v>0.09685393258426966</v>
+        <v>0.07446808510638298</v>
       </c>
       <c r="K3">
-        <v>4.31</v>
+        <v>3.5</v>
       </c>
       <c r="L3">
-        <v>0.09685393258426965</v>
+        <v>0.07446808510638298</v>
       </c>
       <c r="M3">
         <v>4.13</v>
       </c>
       <c r="N3">
-        <v>0.06917922948073701</v>
+        <v>0.07414721723518851</v>
       </c>
       <c r="O3">
-        <v>0.9582366589327147</v>
+        <v>1.18</v>
       </c>
       <c r="P3">
         <v>4.13</v>
       </c>
       <c r="Q3">
-        <v>0.06917922948073701</v>
+        <v>0.07414721723518851</v>
       </c>
       <c r="R3">
-        <v>0.9582366589327147</v>
+        <v>1.18</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,31 +770,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14.2</v>
+        <v>23.7</v>
       </c>
       <c r="V3">
-        <v>0.23785594639866</v>
+        <v>0.4254937163375224</v>
       </c>
       <c r="W3">
-        <v>0.1390322580645161</v>
+        <v>0.1118210862619808</v>
       </c>
       <c r="X3">
-        <v>0.07577902151990337</v>
+        <v>0.1225413288938654</v>
       </c>
       <c r="Y3">
-        <v>0.06325323654461273</v>
+        <v>-0.01072024263188462</v>
       </c>
       <c r="Z3">
-        <v>3.133802816901408</v>
+        <v>2.748538011695906</v>
       </c>
       <c r="AA3">
-        <v>0.3035211267605634</v>
+        <v>0.2046783625730994</v>
       </c>
       <c r="AB3">
-        <v>0.07577902151990337</v>
+        <v>0.1225413288938654</v>
       </c>
       <c r="AC3">
-        <v>0.22774210524066</v>
+        <v>0.08213703367923396</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-14.2</v>
+        <v>-23.7</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,10 +815,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.3120879120879121</v>
+        <v>-0.740625</v>
       </c>
       <c r="AK3">
-        <v>-0.830409356725146</v>
+        <v>-5.266666666666667</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -830,7 +830,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-2.362728785357737</v>
+        <v>-4.85655737704918</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National Insurance Company (ASE:NAAI)</t>
+          <t>Gulf Insurance Group - Jordan (ASE:GIGJ)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,112 +850,118 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.00548</v>
-      </c>
-      <c r="E4">
-        <v>-0.013</v>
+        <v>0.0655</v>
       </c>
       <c r="G4">
-        <v>0.07916666666666668</v>
+        <v>0.16</v>
       </c>
       <c r="H4">
-        <v>0.07916666666666668</v>
+        <v>0.16</v>
       </c>
       <c r="I4">
-        <v>0.09531250000000001</v>
+        <v>0.1072222222222222</v>
       </c>
       <c r="J4">
-        <v>0.08018682065217392</v>
+        <v>0.09159969718145819</v>
       </c>
       <c r="K4">
-        <v>1.55</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="L4">
-        <v>0.08072916666666667</v>
+        <v>0.09133333333333334</v>
       </c>
       <c r="M4">
-        <v>-0</v>
+        <v>1.79</v>
       </c>
       <c r="N4">
-        <v>-0</v>
+        <v>0.02445355191256831</v>
       </c>
       <c r="O4">
-        <v>-0</v>
+        <v>0.2177615571776156</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>1.79</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.02445355191256831</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.2177615571776156</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
+      <c r="T4">
+        <v>0</v>
+      </c>
       <c r="U4">
-        <v>7.93</v>
+        <v>1.66</v>
       </c>
       <c r="V4">
-        <v>0.61</v>
+        <v>0.0226775956284153</v>
       </c>
       <c r="W4">
-        <v>0.12109375</v>
+        <v>0.1437062937062937</v>
       </c>
       <c r="X4">
-        <v>0.07577902151990337</v>
+        <v>0.1250215365583723</v>
       </c>
       <c r="Y4">
-        <v>0.04531472848009663</v>
+        <v>0.01868475714792142</v>
       </c>
       <c r="Z4">
-        <v>3.086816720257234</v>
+        <v>1.740139211136891</v>
       </c>
       <c r="AA4">
-        <v>0.2475220187333986</v>
+        <v>0.1593962247937207</v>
       </c>
       <c r="AB4">
-        <v>0.07577902151990337</v>
+        <v>0.1238106236008529</v>
       </c>
       <c r="AC4">
-        <v>0.1717429972134952</v>
+        <v>0.03558560119286787</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AG4">
-        <v>-7.93</v>
+        <v>1.05</v>
       </c>
       <c r="AH4">
-        <v>0</v>
+        <v>0.03570017125543407</v>
       </c>
       <c r="AI4">
-        <v>0</v>
+        <v>0.03955626915778719</v>
       </c>
       <c r="AJ4">
-        <v>-1.564102564102564</v>
+        <v>0.01414141414141414</v>
       </c>
       <c r="AK4">
-        <v>-1.007623888182973</v>
+        <v>0.01570680628272252</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.023</v>
       </c>
       <c r="AN4">
-        <v>0</v>
+        <v>0.2631067961165048</v>
+      </c>
+      <c r="AO4">
+        <v>419.5652173913044</v>
       </c>
       <c r="AP4">
-        <v>-4.151832460732984</v>
+        <v>0.1019417475728155</v>
+      </c>
+      <c r="AQ4">
+        <v>419.5652173913044</v>
       </c>
     </row>
     <row r="5">
@@ -966,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jordan French Insurance Co. (P.L.C.) (ASE:JOFR)</t>
+          <t>National Insurance Company (ASE:NAAI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -975,46 +981,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0414</v>
+        <v>0.0159</v>
       </c>
       <c r="E5">
-        <v>-0.0735</v>
+        <v>-0.129</v>
       </c>
       <c r="G5">
-        <v>0.07237851662404092</v>
+        <v>0.07545454545454545</v>
       </c>
       <c r="H5">
-        <v>0.07237851662404092</v>
+        <v>0.07545454545454545</v>
       </c>
       <c r="I5">
-        <v>0.05115089514066496</v>
+        <v>0.06818181818181818</v>
       </c>
       <c r="J5">
-        <v>0.03919745066126892</v>
+        <v>0.04954545454545455</v>
       </c>
       <c r="K5">
-        <v>1.43</v>
+        <v>1.09</v>
       </c>
       <c r="L5">
-        <v>0.03657289002557544</v>
+        <v>0.04954545454545455</v>
       </c>
       <c r="M5">
-        <v>0.899</v>
+        <v>1.13</v>
       </c>
       <c r="N5">
-        <v>0.07368852459016394</v>
+        <v>0.0837037037037037</v>
       </c>
       <c r="O5">
-        <v>0.6286713286713287</v>
+        <v>1.036697247706422</v>
       </c>
       <c r="P5">
-        <v>0.899</v>
+        <v>1.13</v>
       </c>
       <c r="Q5">
-        <v>0.07368852459016394</v>
+        <v>0.0837037037037037</v>
       </c>
       <c r="R5">
-        <v>0.6286713286713287</v>
+        <v>1.036697247706422</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1023,73 +1029,67 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>11.2</v>
+        <v>0.35</v>
       </c>
       <c r="V5">
-        <v>0.9180327868852459</v>
+        <v>0.02592592592592593</v>
       </c>
       <c r="W5">
-        <v>0.08313953488372093</v>
+        <v>0.06898734177215191</v>
       </c>
       <c r="X5">
-        <v>0.08600492875309365</v>
+        <v>0.1225413288938654</v>
       </c>
       <c r="Y5">
-        <v>-0.00286539386937272</v>
+        <v>-0.05355398712171354</v>
       </c>
       <c r="Z5">
-        <v>3.969543147208122</v>
+        <v>2.795425667090216</v>
       </c>
       <c r="AA5">
-        <v>0.1555959716604685</v>
+        <v>0.1385006353240152</v>
       </c>
       <c r="AB5">
-        <v>0.07962170577470004</v>
+        <v>0.1225413288938654</v>
       </c>
       <c r="AC5">
-        <v>0.07597426588576847</v>
+        <v>0.0159593064301498</v>
       </c>
       <c r="AD5">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="AG5">
-        <v>-8.629999999999999</v>
+        <v>-0.35</v>
       </c>
       <c r="AH5">
-        <v>0.1740013540961408</v>
+        <v>0</v>
       </c>
       <c r="AI5">
-        <v>0.1255495847581827</v>
+        <v>0</v>
       </c>
       <c r="AJ5">
-        <v>-2.417366946778711</v>
+        <v>-0.02661596958174905</v>
       </c>
       <c r="AK5">
-        <v>-0.930960086299892</v>
+        <v>-0.02127659574468085</v>
       </c>
       <c r="AL5">
-        <v>0.131</v>
+        <v>0</v>
       </c>
       <c r="AM5">
-        <v>0.131</v>
+        <v>0</v>
       </c>
       <c r="AN5">
-        <v>1.189814814814815</v>
-      </c>
-      <c r="AO5">
-        <v>15.26717557251908</v>
+        <v>0</v>
       </c>
       <c r="AP5">
-        <v>-3.99537037037037</v>
-      </c>
-      <c r="AQ5">
-        <v>15.26717557251908</v>
+        <v>-0.2229299363057325</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Middle East Insurance Co. (ASE:MEIN)</t>
+          <t>Jerusalem Insurance Co. (L.T.D) (ASE:JERY)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,46 +1109,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0145</v>
+        <v>0.05309999999999999</v>
       </c>
       <c r="E6">
-        <v>-0.18</v>
+        <v>0.222</v>
       </c>
       <c r="G6">
-        <v>0.05647058823529411</v>
+        <v>0.08829431438127092</v>
       </c>
       <c r="H6">
-        <v>0.05647058823529411</v>
+        <v>0.08829431438127092</v>
       </c>
       <c r="I6">
-        <v>0.1202941176470588</v>
+        <v>0.1016722408026756</v>
       </c>
       <c r="J6">
-        <v>0.08054704595185995</v>
+        <v>0.07176864056659453</v>
       </c>
       <c r="K6">
-        <v>3.06</v>
+        <v>2.16</v>
       </c>
       <c r="L6">
-        <v>0.09</v>
+        <v>0.07224080267558529</v>
       </c>
       <c r="M6">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="N6">
-        <v>0.03919597989949749</v>
+        <v>0.05636363636363637</v>
       </c>
       <c r="O6">
-        <v>0.5098039215686274</v>
+        <v>0.5740740740740741</v>
       </c>
       <c r="P6">
-        <v>1.56</v>
+        <v>1.24</v>
       </c>
       <c r="Q6">
-        <v>0.03919597989949749</v>
+        <v>0.05636363636363637</v>
       </c>
       <c r="R6">
-        <v>0.5098039215686274</v>
+        <v>0.5740740740740741</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1157,70 +1157,67 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>11.7</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="V6">
-        <v>0.2939698492462312</v>
+        <v>0.03704545454545454</v>
       </c>
       <c r="W6">
-        <v>0.05784499054820416</v>
+        <v>0.1064039408866995</v>
       </c>
       <c r="X6">
-        <v>0.0759290420153194</v>
+        <v>0.1225413288938654</v>
       </c>
       <c r="Y6">
-        <v>-0.01808405146711524</v>
+        <v>-0.01613738800716594</v>
       </c>
       <c r="Z6">
-        <v>0.9095286501524796</v>
+        <v>1.554862194487779</v>
       </c>
       <c r="AA6">
-        <v>0.07325984597836493</v>
+        <v>0.1115903459667798</v>
       </c>
       <c r="AB6">
-        <v>0.07586595262157621</v>
+        <v>0.1225413288938654</v>
       </c>
       <c r="AC6">
-        <v>-0.002606106643211273</v>
+        <v>-0.01095098292708561</v>
       </c>
       <c r="AD6">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.123</v>
+        <v>0</v>
       </c>
       <c r="AG6">
-        <v>-11.577</v>
+        <v>-0.8149999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.003080930791774166</v>
+        <v>0</v>
       </c>
       <c r="AI6">
-        <v>0.002149485346801111</v>
+        <v>0</v>
       </c>
       <c r="AJ6">
-        <v>-0.4101973567657584</v>
+        <v>-0.03847061600188813</v>
       </c>
       <c r="AK6">
-        <v>-0.2543110076225205</v>
+        <v>-0.04119282284559009</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-0.003</v>
+        <v>0</v>
       </c>
       <c r="AN6">
-        <v>0.02494929006085193</v>
+        <v>0</v>
       </c>
       <c r="AP6">
-        <v>-2.348275862068966</v>
-      </c>
-      <c r="AQ6">
-        <v>-1363.333333333333</v>
+        <v>-0.2531055900621118</v>
       </c>
     </row>
     <row r="7">
@@ -1231,7 +1228,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Jordan Insurance Company (ASE:JOIN)</t>
+          <t>First Insurance Company (ASE:FINS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1240,118 +1237,115 @@
         </is>
       </c>
       <c r="D7">
-        <v>-0.0107</v>
+        <v>0.0649</v>
       </c>
       <c r="E7">
-        <v>0.0172</v>
+        <v>0.06269999999999999</v>
       </c>
       <c r="G7">
-        <v>0.11309963099631</v>
+        <v>0.0872093023255814</v>
       </c>
       <c r="H7">
-        <v>0.11309963099631</v>
+        <v>0.0872093023255814</v>
       </c>
       <c r="I7">
-        <v>0.06309963099630995</v>
+        <v>0.08581395348837209</v>
       </c>
       <c r="J7">
-        <v>0.05464297941948491</v>
+        <v>0.08051162790697675</v>
       </c>
       <c r="K7">
-        <v>1.68</v>
+        <v>3.46</v>
       </c>
       <c r="L7">
-        <v>0.03099630996309963</v>
+        <v>0.08046511627906977</v>
       </c>
       <c r="M7">
-        <v>-0</v>
+        <v>2.51</v>
       </c>
       <c r="N7">
-        <v>-0</v>
+        <v>0.09507575757575758</v>
       </c>
       <c r="O7">
-        <v>-0</v>
+        <v>0.7254335260115606</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>2.51</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.09507575757575758</v>
       </c>
       <c r="R7">
-        <v>-0</v>
+        <v>0.7254335260115606</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
       <c r="U7">
-        <v>5.43</v>
+        <v>15.8</v>
       </c>
       <c r="V7">
-        <v>0.09034941763727121</v>
+        <v>0.5984848484848485</v>
       </c>
       <c r="W7">
-        <v>0.02994652406417112</v>
+        <v>0.07393162393162393</v>
       </c>
       <c r="X7">
-        <v>0.09629479052629998</v>
+        <v>0.1225413288938654</v>
       </c>
       <c r="Y7">
-        <v>-0.06634826646212885</v>
+        <v>-0.04860970496224151</v>
       </c>
       <c r="Z7">
-        <v>1.358395989974937</v>
+        <v>1.08366935483871</v>
       </c>
       <c r="AA7">
-        <v>0.07422680412371134</v>
+        <v>0.08724798387096774</v>
       </c>
       <c r="AB7">
-        <v>0.08416127602006598</v>
+        <v>0.1225413288938654</v>
       </c>
       <c r="AC7">
-        <v>-0.009934471896354644</v>
+        <v>-0.0352933450228977</v>
       </c>
       <c r="AD7">
-        <v>25.4</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>25.4</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>19.97</v>
+        <v>-15.8</v>
       </c>
       <c r="AH7">
-        <v>0.2970760233918128</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.2659685863874345</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>0.2494067690770576</v>
+        <v>-1.490566037735849</v>
       </c>
       <c r="AK7">
-        <v>0.221716442766737</v>
+        <v>-0.4922118380062306</v>
       </c>
       <c r="AL7">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AM7">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN7">
-        <v>6.71957671957672</v>
-      </c>
-      <c r="AO7">
-        <v>2.780487804878049</v>
+        <v>0</v>
       </c>
       <c r="AP7">
-        <v>5.283068783068783</v>
-      </c>
-      <c r="AQ7">
-        <v>2.780487804878049</v>
+        <v>-3.657407407407407</v>
       </c>
     </row>
     <row r="8">
@@ -1362,7 +1356,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Arabia Insurance Company - Jordan (ASE:AICJ)</t>
+          <t>Middle East Insurance Co. (ASE:MEIN)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1371,112 +1365,121 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0142</v>
+        <v>0.0196</v>
       </c>
       <c r="E8">
-        <v>-0.149</v>
+        <v>0.225</v>
       </c>
       <c r="G8">
-        <v>0.06728971962616823</v>
+        <v>0.1372492836676218</v>
       </c>
       <c r="H8">
-        <v>0.06728971962616823</v>
+        <v>0.1372492836676218</v>
       </c>
       <c r="I8">
-        <v>0.03</v>
+        <v>0.1418338108882522</v>
       </c>
       <c r="J8">
-        <v>0.02313084112149533</v>
+        <v>0.1054083094555874</v>
       </c>
       <c r="K8">
-        <v>0.495</v>
+        <v>3.27</v>
       </c>
       <c r="L8">
-        <v>0.02313084112149533</v>
+        <v>0.09369627507163324</v>
       </c>
       <c r="M8">
-        <v>-0</v>
+        <v>1.547</v>
       </c>
       <c r="N8">
-        <v>-0</v>
+        <v>0.04789473684210527</v>
       </c>
       <c r="O8">
-        <v>-0</v>
+        <v>0.4730886850152906</v>
       </c>
       <c r="P8">
-        <v>-0</v>
+        <v>1.547</v>
       </c>
       <c r="Q8">
-        <v>-0</v>
+        <v>0.04789473684210527</v>
       </c>
       <c r="R8">
-        <v>-0</v>
+        <v>0.4730886850152906</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
       <c r="U8">
-        <v>3.61</v>
+        <v>13</v>
       </c>
       <c r="V8">
-        <v>0.542042042042042</v>
+        <v>0.4024767801857586</v>
       </c>
       <c r="W8">
-        <v>0.0336734693877551</v>
+        <v>0.05726795096322242</v>
       </c>
       <c r="X8">
-        <v>0.07577902151990337</v>
+        <v>0.1226699223896282</v>
       </c>
       <c r="Y8">
-        <v>-0.04210555213214827</v>
+        <v>-0.06540197142640576</v>
       </c>
       <c r="Z8">
-        <v>2.819499341238472</v>
+        <v>0.766645431979439</v>
       </c>
       <c r="AA8">
-        <v>0.06521739130434784</v>
+        <v>0.08081079893680118</v>
       </c>
       <c r="AB8">
-        <v>0.07577902151990337</v>
+        <v>0.1226094447948534</v>
       </c>
       <c r="AC8">
-        <v>-0.01056163021555553</v>
+        <v>-0.04179864585805221</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>0.062</v>
       </c>
       <c r="AG8">
-        <v>-3.61</v>
+        <v>-12.938</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>0.001915827204746308</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>0.001005481495896987</v>
       </c>
       <c r="AJ8">
-        <v>-1.183606557377049</v>
+        <v>-0.6682160933787834</v>
       </c>
       <c r="AK8">
-        <v>-0.3061916878710771</v>
+        <v>-0.2658748099132794</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>0.006</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>0.01067125645438899</v>
+      </c>
+      <c r="AO8">
+        <v>825</v>
       </c>
       <c r="AP8">
-        <v>-4.242068155111633</v>
+        <v>-2.22685025817556</v>
+      </c>
+      <c r="AQ8">
+        <v>825</v>
       </c>
     </row>
     <row r="9">
@@ -1487,7 +1490,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>First Insurance Company (ASE:FINS)</t>
+          <t>Arab Assurers Insurance Company (ASE:ARAS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1496,103 +1499,100 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0554</v>
+        <v>0.04019999999999999</v>
       </c>
       <c r="E9">
-        <v>-0.04190000000000001</v>
+        <v>-0.119</v>
       </c>
       <c r="G9">
-        <v>0.08306878306878308</v>
+        <v>-0.1062176165803109</v>
       </c>
       <c r="H9">
-        <v>0.08306878306878308</v>
+        <v>-0.1062176165803109</v>
       </c>
       <c r="I9">
-        <v>0.07724867724867725</v>
+        <v>0.01694300518134715</v>
       </c>
       <c r="J9">
-        <v>0.05997354497354497</v>
+        <v>0.01694300518134715</v>
       </c>
       <c r="K9">
-        <v>2.27</v>
+        <v>0.539</v>
       </c>
       <c r="L9">
-        <v>0.06005291005291006</v>
+        <v>0.02792746113989637</v>
       </c>
       <c r="M9">
-        <v>1.73</v>
+        <v>-0</v>
       </c>
       <c r="N9">
-        <v>0.06628352490421456</v>
+        <v>-0</v>
       </c>
       <c r="O9">
-        <v>0.762114537444934</v>
+        <v>-0</v>
       </c>
       <c r="P9">
-        <v>1.73</v>
+        <v>-0</v>
       </c>
       <c r="Q9">
-        <v>0.06628352490421456</v>
+        <v>-0</v>
       </c>
       <c r="R9">
-        <v>0.762114537444934</v>
+        <v>-0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
-      <c r="T9">
-        <v>0</v>
-      </c>
       <c r="U9">
-        <v>10.4</v>
+        <v>2.7</v>
       </c>
       <c r="V9">
-        <v>0.3984674329501915</v>
+        <v>1.298076923076923</v>
       </c>
       <c r="W9">
-        <v>0.05</v>
+        <v>0.0695483870967742</v>
       </c>
       <c r="X9">
-        <v>0.07577902151990337</v>
+        <v>0.128403221916436</v>
       </c>
       <c r="Y9">
-        <v>-0.02577902151990337</v>
+        <v>-0.05885483481966185</v>
       </c>
       <c r="Z9">
-        <v>0.961587382345459</v>
+        <v>4.862685815066768</v>
       </c>
       <c r="AA9">
-        <v>0.05766980412108878</v>
+        <v>0.08238851095993954</v>
       </c>
       <c r="AB9">
-        <v>0.07577902151990337</v>
+        <v>0.1246617900570834</v>
       </c>
       <c r="AC9">
-        <v>-0.0181092173988146</v>
+        <v>-0.0422732790971439</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>0.182</v>
       </c>
       <c r="AG9">
-        <v>-10.4</v>
+        <v>-2.518</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>0.08045977011494253</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>0.02202856451222464</v>
       </c>
       <c r="AJ9">
-        <v>-0.6624203821656051</v>
+        <v>5.748858447488582</v>
       </c>
       <c r="AK9">
-        <v>-0.2833787465940054</v>
+        <v>-0.4527148507731033</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1601,10 +1601,10 @@
         <v>0</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>0.4312796208530806</v>
       </c>
       <c r="AP9">
-        <v>-2.896935933147633</v>
+        <v>-5.966824644549764</v>
       </c>
     </row>
     <row r="10">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jordan International Insurance Company (ASE:JIJC)</t>
+          <t>Jordan Insurance Company (ASE:JOIN)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1624,109 +1624,118 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.05110000000000001</v>
+        <v>-0.0268</v>
       </c>
       <c r="G10">
-        <v>-0.04311688311688312</v>
+        <v>0.06802218114602587</v>
       </c>
       <c r="H10">
-        <v>-0.04311688311688312</v>
+        <v>0.06802218114602587</v>
       </c>
       <c r="I10">
-        <v>-0.04305194805194806</v>
+        <v>0.04842883548983364</v>
       </c>
       <c r="J10">
-        <v>-0.04305194805194806</v>
+        <v>0.02421441774491682</v>
       </c>
       <c r="K10">
-        <v>-0.169</v>
+        <v>0.376</v>
       </c>
       <c r="L10">
-        <v>-0.01097402597402597</v>
+        <v>0.006950092421441774</v>
       </c>
       <c r="M10">
-        <v>-0</v>
+        <v>3.39</v>
       </c>
       <c r="N10">
-        <v>-0</v>
+        <v>0.06075268817204302</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>9.01595744680851</v>
       </c>
       <c r="P10">
-        <v>-0</v>
+        <v>3.39</v>
       </c>
       <c r="Q10">
-        <v>-0</v>
+        <v>0.06075268817204302</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>9.01595744680851</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
+      <c r="T10">
+        <v>0</v>
+      </c>
       <c r="U10">
-        <v>13</v>
+        <v>40.3</v>
       </c>
       <c r="V10">
-        <v>1.371308016877637</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="W10">
-        <v>-0.005633333333333334</v>
+        <v>0.005363766048502141</v>
       </c>
       <c r="X10">
-        <v>0.07577902151990337</v>
+        <v>0.1418708686098688</v>
       </c>
       <c r="Y10">
-        <v>-0.08141235485323671</v>
+        <v>-0.1365071025613667</v>
       </c>
       <c r="Z10">
-        <v>0.7176141658900279</v>
+        <v>0.6006439435994227</v>
       </c>
       <c r="AA10">
-        <v>-0.03089468779123952</v>
+        <v>0.01454424336627068</v>
       </c>
       <c r="AB10">
-        <v>0.07577902151990337</v>
+        <v>0.1305027235914999</v>
       </c>
       <c r="AC10">
-        <v>-0.1066737093111429</v>
+        <v>-0.1159584802252292</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="AG10">
-        <v>-13</v>
+        <v>-24.2</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>0.2239221140472879</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>0.212962962962963</v>
       </c>
       <c r="AJ10">
-        <v>3.693181818181819</v>
+        <v>-0.7658227848101264</v>
       </c>
       <c r="AK10">
-        <v>-0.7558139534883721</v>
+        <v>-0.6855524079320111</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AN10">
-        <v>-0</v>
+        <v>5.127388535031847</v>
+      </c>
+      <c r="AO10">
+        <v>1.253588516746412</v>
       </c>
       <c r="AP10">
-        <v>28.9532293986637</v>
+        <v>-7.70700636942675</v>
+      </c>
+      <c r="AQ10">
+        <v>1.253588516746412</v>
       </c>
     </row>
     <row r="11">
@@ -1737,7 +1746,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>The Mediterranean &amp; Gulf Insurance Co P L C - Jordan (ASE:MDGF)</t>
+          <t>Arab Union International Insurance PLC (ASE:AIUI)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1745,26 +1754,8 @@
           <t>Insurance (General)</t>
         </is>
       </c>
-      <c r="D11">
-        <v>-0.0143</v>
-      </c>
-      <c r="G11">
-        <v>-0.02367713004484305</v>
-      </c>
-      <c r="H11">
-        <v>-0.02367713004484305</v>
-      </c>
-      <c r="I11">
-        <v>-0.01443946188340807</v>
-      </c>
-      <c r="J11">
-        <v>-0.01443946188340807</v>
-      </c>
       <c r="K11">
-        <v>-0.347</v>
-      </c>
-      <c r="L11">
-        <v>-0.01556053811659193</v>
+        <v>0</v>
       </c>
       <c r="M11">
         <v>-0</v>
@@ -1772,89 +1763,315 @@
       <c r="N11">
         <v>-0</v>
       </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
       <c r="P11">
         <v>-0</v>
       </c>
       <c r="Q11">
         <v>-0</v>
       </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
       <c r="S11">
         <v>0</v>
       </c>
       <c r="U11">
-        <v>6.37</v>
+        <v>1.24</v>
       </c>
       <c r="V11">
-        <v>0.6447368421052632</v>
+        <v>0.2995169082125604</v>
       </c>
       <c r="W11">
-        <v>-0.04714673913043477</v>
+        <v>0</v>
       </c>
       <c r="X11">
-        <v>0.07587728714179795</v>
+        <v>0.1225413288938654</v>
       </c>
       <c r="Y11">
-        <v>-0.1230240262722327</v>
+        <v>-0.1225413288938654</v>
       </c>
       <c r="Z11">
-        <v>9.40531421341206</v>
+        <v>0</v>
       </c>
       <c r="AA11">
-        <v>-0.1358076760860396</v>
+        <v>0</v>
       </c>
       <c r="AB11">
-        <v>0.07582363610658209</v>
+        <v>0.1225413288938654</v>
       </c>
       <c r="AC11">
-        <v>-0.2116313121926217</v>
+        <v>-0.1225413288938654</v>
       </c>
       <c r="AD11">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AE11">
         <v>0</v>
       </c>
       <c r="AF11">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="AG11">
-        <v>-6.350000000000001</v>
+        <v>-1.24</v>
       </c>
       <c r="AH11">
-        <v>0.00202020202020202</v>
+        <v>0</v>
       </c>
       <c r="AI11">
-        <v>0.002861230329041488</v>
+        <v>0</v>
       </c>
       <c r="AJ11">
-        <v>-1.798866855524079</v>
+        <v>-0.4275862068965518</v>
       </c>
       <c r="AK11">
-        <v>-10.24193548387098</v>
+        <v>-0.3583815028901734</v>
       </c>
       <c r="AL11">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AM11">
-        <v>0.004</v>
-      </c>
-      <c r="AN11">
-        <v>-0.2777777777777778</v>
-      </c>
-      <c r="AO11">
-        <v>-80.5</v>
-      </c>
-      <c r="AP11">
-        <v>88.19444444444446</v>
-      </c>
-      <c r="AQ11">
-        <v>-80.5</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Arabia Insurance Company - Jordan (ASE:AICJ)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>0.0285</v>
+      </c>
+      <c r="G12">
+        <v>-0.02698347107438017</v>
+      </c>
+      <c r="H12">
+        <v>-0.02698347107438017</v>
+      </c>
+      <c r="I12">
+        <v>-0.006115702479338843</v>
+      </c>
+      <c r="J12">
+        <v>-0.006115702479338843</v>
+      </c>
+      <c r="K12">
+        <v>-0.154</v>
+      </c>
+      <c r="L12">
+        <v>-0.006363636363636364</v>
+      </c>
+      <c r="M12">
+        <v>-0</v>
+      </c>
+      <c r="N12">
+        <v>-0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>-0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>4.17</v>
+      </c>
+      <c r="V12">
+        <v>0.5366795366795367</v>
+      </c>
+      <c r="W12">
+        <v>-0.01</v>
+      </c>
+      <c r="X12">
+        <v>0.1225413288938654</v>
+      </c>
+      <c r="Y12">
+        <v>-0.1325413288938654</v>
+      </c>
+      <c r="Z12">
+        <v>2.052586938083121</v>
+      </c>
+      <c r="AA12">
+        <v>-0.01255301102629347</v>
+      </c>
+      <c r="AB12">
+        <v>0.1225413288938654</v>
+      </c>
+      <c r="AC12">
+        <v>-0.1350943399201589</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>-4.17</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>-1.158333333333333</v>
+      </c>
+      <c r="AK12">
+        <v>-0.3746630727762803</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>-85.10204081632652</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Jordan International Insurance Company (ASE:JIJC)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Insurance (General)</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>0.0254</v>
+      </c>
+      <c r="G13">
+        <v>-0.004875</v>
+      </c>
+      <c r="H13">
+        <v>-0.004875</v>
+      </c>
+      <c r="I13">
+        <v>-0.08749999999999999</v>
+      </c>
+      <c r="J13">
+        <v>-0.08749999999999999</v>
+      </c>
+      <c r="K13">
+        <v>-1.64</v>
+      </c>
+      <c r="L13">
+        <v>-0.1025</v>
+      </c>
+      <c r="M13">
+        <v>-0</v>
+      </c>
+      <c r="N13">
+        <v>-0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>-0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>9.02</v>
+      </c>
+      <c r="V13">
+        <v>1.176010430247718</v>
+      </c>
+      <c r="W13">
+        <v>-0.05655172413793103</v>
+      </c>
+      <c r="X13">
+        <v>0.1319745111838654</v>
+      </c>
+      <c r="Y13">
+        <v>-0.1885262353217964</v>
+      </c>
+      <c r="Z13">
+        <v>1</v>
+      </c>
+      <c r="AA13">
+        <v>-0.08749999999999999</v>
+      </c>
+      <c r="AB13">
+        <v>0.1257942028676771</v>
+      </c>
+      <c r="AC13">
+        <v>-0.2132942028676771</v>
+      </c>
+      <c r="AD13">
+        <v>1.08</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>1.08</v>
+      </c>
+      <c r="AG13">
+        <v>-7.94</v>
+      </c>
+      <c r="AH13">
+        <v>0.1234285714285714</v>
+      </c>
+      <c r="AI13">
+        <v>0.03805496828752643</v>
+      </c>
+      <c r="AJ13">
+        <v>29.40740740740745</v>
+      </c>
+      <c r="AK13">
+        <v>-0.4101239669421488</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>-0.870967741935484</v>
+      </c>
+      <c r="AP13">
+        <v>6.403225806451613</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jordan/jordan_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_insurance_general.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ13"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.03435</v>
+        <v>0.0377</v>
       </c>
       <c r="E2">
-        <v>0.05125</v>
+        <v>0.056235</v>
       </c>
       <c r="G2">
-        <v>0.08903522607781283</v>
+        <v>0.03836809470124014</v>
       </c>
       <c r="H2">
-        <v>0.08903522607781283</v>
+        <v>0.03836809470124014</v>
       </c>
       <c r="I2">
-        <v>0.07562828601472135</v>
+        <v>0.06716178128523112</v>
       </c>
       <c r="J2">
-        <v>0.06352201954263204</v>
+        <v>0.05568734778466795</v>
       </c>
       <c r="K2">
-        <v>20.821</v>
+        <v>17.624</v>
       </c>
       <c r="L2">
-        <v>0.05473449001051525</v>
+        <v>0.04967305524239007</v>
       </c>
       <c r="M2">
-        <v>15.737</v>
+        <v>9.894</v>
       </c>
       <c r="N2">
-        <v>0.0523589299973383</v>
+        <v>0.05059316833708325</v>
       </c>
       <c r="O2">
-        <v>0.7558234474809087</v>
+        <v>0.5613935542442124</v>
       </c>
       <c r="P2">
-        <v>15.737</v>
+        <v>9.894</v>
       </c>
       <c r="Q2">
-        <v>0.0523589299973383</v>
+        <v>0.05059316833708325</v>
       </c>
       <c r="R2">
-        <v>0.7558234474809087</v>
+        <v>0.5613935542442124</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>112.755</v>
+        <v>79.97</v>
       </c>
       <c r="V2">
-        <v>0.3751497205216928</v>
+        <v>0.4089282061771323</v>
       </c>
       <c r="W2">
-        <v>0.06898734177215191</v>
+        <v>0.04435189075630252</v>
       </c>
       <c r="X2">
-        <v>0.1225413288938654</v>
+        <v>0.1086611138607355</v>
       </c>
       <c r="Y2">
-        <v>-0.05355398712171354</v>
+        <v>-0.06430922310443299</v>
       </c>
       <c r="Z2">
-        <v>1.234455723149614</v>
+        <v>1.915353055495574</v>
       </c>
       <c r="AA2">
-        <v>0.08238851095993954</v>
+        <v>0.09095825863788282</v>
       </c>
       <c r="AB2">
-        <v>0.1225413288938654</v>
+        <v>0.108543675842813</v>
       </c>
       <c r="AC2">
-        <v>-0.04179864585805221</v>
+        <v>-0.02025611097574105</v>
       </c>
       <c r="AD2">
-        <v>20.134</v>
+        <v>13.463</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>20.134</v>
+        <v>13.463</v>
       </c>
       <c r="AG2">
-        <v>-92.621</v>
+        <v>-66.50700000000001</v>
       </c>
       <c r="AH2">
-        <v>0.06278259025737931</v>
+        <v>0.06440917985102118</v>
       </c>
       <c r="AI2">
-        <v>0.05356012279404332</v>
+        <v>0.05057608577235313</v>
       </c>
       <c r="AJ2">
-        <v>-0.4454238983548059</v>
+        <v>-0.5153464080649036</v>
       </c>
       <c r="AK2">
-        <v>-0.3519583217750485</v>
+        <v>-0.3571363365427471</v>
       </c>
       <c r="AL2">
-        <v>2.119</v>
+        <v>0.892</v>
       </c>
       <c r="AM2">
-        <v>2.119</v>
+        <v>0.791</v>
       </c>
       <c r="AN2">
-        <v>0.6200609774876042</v>
+        <v>0.5095375066232685</v>
       </c>
       <c r="AO2">
-        <v>13.57668711656442</v>
+        <v>26.71412556053812</v>
       </c>
       <c r="AP2">
-        <v>-2.852422161313172</v>
+        <v>-2.517106956324275</v>
       </c>
       <c r="AQ2">
-        <v>13.57668711656442</v>
+        <v>30.12515802781289</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Al-Nisr Al-Arabi Insurance Company (ASE:AAIN)</t>
+          <t>National Insurance Company (ASE:NAAI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,46 +722,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0761</v>
-      </c>
-      <c r="E3">
-        <v>0.0398</v>
+        <v>0.0322</v>
       </c>
       <c r="G3">
-        <v>0.1219148936170213</v>
+        <v>0.07598566308243729</v>
       </c>
       <c r="H3">
-        <v>0.1219148936170213</v>
+        <v>0.07598566308243729</v>
       </c>
       <c r="I3">
-        <v>0.09659574468085107</v>
+        <v>0.0978494623655914</v>
       </c>
       <c r="J3">
-        <v>0.07446808510638298</v>
+        <v>0.07415959252971138</v>
       </c>
       <c r="K3">
-        <v>3.5</v>
+        <v>2.16</v>
       </c>
       <c r="L3">
-        <v>0.07446808510638298</v>
+        <v>0.07741935483870968</v>
       </c>
       <c r="M3">
-        <v>4.13</v>
+        <v>1.13</v>
       </c>
       <c r="N3">
-        <v>0.07414721723518851</v>
+        <v>0.08071428571428571</v>
       </c>
       <c r="O3">
-        <v>1.18</v>
+        <v>0.523148148148148</v>
       </c>
       <c r="P3">
-        <v>4.13</v>
+        <v>1.13</v>
       </c>
       <c r="Q3">
-        <v>0.07414721723518851</v>
+        <v>0.08071428571428571</v>
       </c>
       <c r="R3">
-        <v>1.18</v>
+        <v>0.523148148148148</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>23.7</v>
+        <v>5.73</v>
       </c>
       <c r="V3">
-        <v>0.4254937163375224</v>
+        <v>0.4092857142857143</v>
       </c>
       <c r="W3">
-        <v>0.1118210862619808</v>
+        <v>0.1285714285714286</v>
       </c>
       <c r="X3">
-        <v>0.1225413288938654</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="Y3">
-        <v>-0.01072024263188462</v>
+        <v>0.0201571787876095</v>
       </c>
       <c r="Z3">
-        <v>2.748538011695906</v>
+        <v>3.618677042801556</v>
       </c>
       <c r="AA3">
-        <v>0.2046783625730994</v>
+        <v>0.2683596149907843</v>
       </c>
       <c r="AB3">
-        <v>0.1225413288938654</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="AC3">
-        <v>0.08213703367923396</v>
+        <v>0.1599453652069652</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-23.7</v>
+        <v>-5.73</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,10 +812,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.740625</v>
+        <v>-0.6928657799274487</v>
       </c>
       <c r="AK3">
-        <v>-5.266666666666667</v>
+        <v>-0.5084294587400178</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -830,7 +827,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-4.85655737704918</v>
+        <v>-2.046428571428572</v>
       </c>
     </row>
     <row r="4">
@@ -850,43 +847,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0655</v>
+        <v>0.0429</v>
+      </c>
+      <c r="E4">
+        <v>0.951</v>
       </c>
       <c r="G4">
-        <v>0.16</v>
+        <v>0.1251325556733828</v>
       </c>
       <c r="H4">
-        <v>0.16</v>
+        <v>0.1251325556733828</v>
       </c>
       <c r="I4">
-        <v>0.1072222222222222</v>
+        <v>0.1452810180275716</v>
       </c>
       <c r="J4">
-        <v>0.09159969718145819</v>
+        <v>0.1420572640509014</v>
       </c>
       <c r="K4">
-        <v>8.220000000000001</v>
+        <v>13.4</v>
       </c>
       <c r="L4">
-        <v>0.09133333333333334</v>
+        <v>0.1420996818663839</v>
       </c>
       <c r="M4">
-        <v>1.79</v>
+        <v>5.5</v>
       </c>
       <c r="N4">
-        <v>0.02445355191256831</v>
+        <v>0.08435582822085889</v>
       </c>
       <c r="O4">
-        <v>0.2177615571776156</v>
+        <v>0.4104477611940298</v>
       </c>
       <c r="P4">
-        <v>1.79</v>
+        <v>5.5</v>
       </c>
       <c r="Q4">
-        <v>0.02445355191256831</v>
+        <v>0.08435582822085889</v>
       </c>
       <c r="R4">
-        <v>0.2177615571776156</v>
+        <v>0.4104477611940298</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -895,73 +895,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="V4">
-        <v>0.0226775956284153</v>
+        <v>0.02024539877300614</v>
       </c>
       <c r="W4">
-        <v>0.1437062937062937</v>
+        <v>0.2036474164133739</v>
       </c>
       <c r="X4">
-        <v>0.1250215365583723</v>
+        <v>0.1086909984578063</v>
       </c>
       <c r="Y4">
-        <v>0.01868475714792142</v>
+        <v>0.09495641795556757</v>
       </c>
       <c r="Z4">
-        <v>1.740139211136891</v>
+        <v>1.410620792819746</v>
       </c>
       <c r="AA4">
-        <v>0.1593962247937207</v>
+        <v>0.2003889304412865</v>
       </c>
       <c r="AB4">
-        <v>0.1238106236008529</v>
+        <v>0.1085592756228217</v>
       </c>
       <c r="AC4">
-        <v>0.03558560119286787</v>
+        <v>0.09182965481846478</v>
       </c>
       <c r="AD4">
-        <v>2.71</v>
+        <v>0.324</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>2.71</v>
+        <v>0.324</v>
       </c>
       <c r="AG4">
-        <v>1.05</v>
+        <v>-0.996</v>
       </c>
       <c r="AH4">
-        <v>0.03570017125543407</v>
+        <v>0.004944753067578292</v>
       </c>
       <c r="AI4">
-        <v>0.03955626915778719</v>
+        <v>0.005005871083369384</v>
       </c>
       <c r="AJ4">
-        <v>0.01414141414141414</v>
+        <v>-0.01551305214628372</v>
       </c>
       <c r="AK4">
-        <v>0.01570680628272252</v>
+        <v>-0.01570878808907955</v>
       </c>
       <c r="AL4">
-        <v>0.023</v>
+        <v>0.044</v>
       </c>
       <c r="AM4">
-        <v>0.023</v>
+        <v>0.044</v>
       </c>
       <c r="AN4">
-        <v>0.2631067961165048</v>
+        <v>0.02219178082191781</v>
       </c>
       <c r="AO4">
-        <v>419.5652173913044</v>
+        <v>311.3636363636364</v>
       </c>
       <c r="AP4">
-        <v>0.1019417475728155</v>
+        <v>-0.06821917808219179</v>
       </c>
       <c r="AQ4">
-        <v>419.5652173913044</v>
+        <v>311.3636363636364</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +972,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Insurance Company (ASE:NAAI)</t>
+          <t>First Insurance Company (ASE:FINS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,46 +981,46 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0159</v>
+        <v>0.103</v>
       </c>
       <c r="E5">
-        <v>-0.129</v>
+        <v>-0.00053</v>
       </c>
       <c r="G5">
-        <v>0.07545454545454545</v>
+        <v>0.08216318785578747</v>
       </c>
       <c r="H5">
-        <v>0.07545454545454545</v>
+        <v>0.08216318785578747</v>
       </c>
       <c r="I5">
-        <v>0.06818181818181818</v>
+        <v>0.08899430740037952</v>
       </c>
       <c r="J5">
-        <v>0.04954545454545455</v>
+        <v>0.07149905123339659</v>
       </c>
       <c r="K5">
-        <v>1.09</v>
+        <v>3.77</v>
       </c>
       <c r="L5">
-        <v>0.04954545454545455</v>
+        <v>0.0715370018975332</v>
       </c>
       <c r="M5">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="N5">
-        <v>0.0837037037037037</v>
+        <v>0.05266666666666667</v>
       </c>
       <c r="O5">
-        <v>1.036697247706422</v>
+        <v>0.4190981432360743</v>
       </c>
       <c r="P5">
-        <v>1.13</v>
+        <v>1.58</v>
       </c>
       <c r="Q5">
-        <v>0.0837037037037037</v>
+        <v>0.05266666666666667</v>
       </c>
       <c r="R5">
-        <v>1.036697247706422</v>
+        <v>0.4190981432360743</v>
       </c>
       <c r="S5">
         <v>0</v>
@@ -1029,55 +1029,55 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>0.35</v>
+        <v>18.1</v>
       </c>
       <c r="V5">
-        <v>0.02592592592592593</v>
+        <v>0.6033333333333334</v>
       </c>
       <c r="W5">
-        <v>0.06898734177215191</v>
+        <v>0.07870563674321504</v>
       </c>
       <c r="X5">
-        <v>0.1225413288938654</v>
+        <v>0.1097118593997895</v>
       </c>
       <c r="Y5">
-        <v>-0.05355398712171354</v>
+        <v>-0.03100622265657443</v>
       </c>
       <c r="Z5">
-        <v>2.795425667090216</v>
+        <v>1.641744548286605</v>
       </c>
       <c r="AA5">
-        <v>0.1385006353240152</v>
+        <v>0.1173831775700935</v>
       </c>
       <c r="AB5">
-        <v>0.1225413288938654</v>
+        <v>0.1090820610246334</v>
       </c>
       <c r="AC5">
-        <v>0.0159593064301498</v>
+        <v>0.008301116545460077</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>0.699</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>0.699</v>
       </c>
       <c r="AG5">
-        <v>-0.35</v>
+        <v>-17.401</v>
       </c>
       <c r="AH5">
-        <v>0</v>
+        <v>0.02276947131828398</v>
       </c>
       <c r="AI5">
-        <v>0</v>
+        <v>0.01459320653875864</v>
       </c>
       <c r="AJ5">
-        <v>-0.02661596958174905</v>
+        <v>-1.381141360425431</v>
       </c>
       <c r="AK5">
-        <v>-0.02127659574468085</v>
+        <v>-0.5839457699922815</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1086,10 +1086,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>0</v>
+        <v>0.1321361058601134</v>
       </c>
       <c r="AP5">
-        <v>-0.2229299363057325</v>
+        <v>-3.289413988657845</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1100,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Jerusalem Insurance Co. (L.T.D) (ASE:JERY)</t>
+          <t>Jordan French Insurance Co. (P.L.C.) (ASE:JOFR)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1109,46 +1109,46 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.05309999999999999</v>
+        <v>0.0767</v>
       </c>
       <c r="E6">
-        <v>0.222</v>
+        <v>-0.0235</v>
       </c>
       <c r="G6">
-        <v>0.08829431438127092</v>
+        <v>-0.03092369477911647</v>
       </c>
       <c r="H6">
-        <v>0.08829431438127092</v>
+        <v>-0.03092369477911647</v>
       </c>
       <c r="I6">
-        <v>0.1016722408026756</v>
+        <v>0.03313253012048193</v>
       </c>
       <c r="J6">
-        <v>0.07176864056659453</v>
+        <v>0.02665941543953592</v>
       </c>
       <c r="K6">
-        <v>2.16</v>
+        <v>0.868</v>
       </c>
       <c r="L6">
-        <v>0.07224080267558529</v>
+        <v>0.01742971887550201</v>
       </c>
       <c r="M6">
-        <v>1.24</v>
+        <v>0.004</v>
       </c>
       <c r="N6">
-        <v>0.05636363636363637</v>
+        <v>0.0005194805194805195</v>
       </c>
       <c r="O6">
-        <v>0.5740740740740741</v>
+        <v>0.004608294930875576</v>
       </c>
       <c r="P6">
-        <v>1.24</v>
+        <v>0.004</v>
       </c>
       <c r="Q6">
-        <v>0.05636363636363637</v>
+        <v>0.0005194805194805195</v>
       </c>
       <c r="R6">
-        <v>0.5740740740740741</v>
+        <v>0.004608294930875576</v>
       </c>
       <c r="S6">
         <v>0</v>
@@ -1157,67 +1157,73 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>0.8149999999999999</v>
+        <v>4.37</v>
       </c>
       <c r="V6">
-        <v>0.03704545454545454</v>
+        <v>0.5675324675324676</v>
       </c>
       <c r="W6">
-        <v>0.1064039408866995</v>
+        <v>0.05425</v>
       </c>
       <c r="X6">
-        <v>0.1225413288938654</v>
+        <v>0.1086312292636648</v>
       </c>
       <c r="Y6">
-        <v>-0.01613738800716594</v>
+        <v>-0.05438122926366475</v>
       </c>
       <c r="Z6">
-        <v>1.554862194487779</v>
+        <v>3.875486381322957</v>
       </c>
       <c r="AA6">
-        <v>0.1115903459667798</v>
+        <v>0.1033182014699524</v>
       </c>
       <c r="AB6">
-        <v>0.1225413288938654</v>
+        <v>0.1085280760628044</v>
       </c>
       <c r="AC6">
-        <v>-0.01095098292708561</v>
+        <v>-0.005209874592851937</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="AG6">
-        <v>-0.8149999999999999</v>
+        <v>-4.34</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>0.003880983182406209</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>0.001772002362669817</v>
       </c>
       <c r="AJ6">
-        <v>-0.03847061600188813</v>
+        <v>-1.291666666666667</v>
       </c>
       <c r="AK6">
-        <v>-0.04119282284559009</v>
+        <v>-0.3455414012738854</v>
       </c>
       <c r="AL6">
-        <v>0</v>
+        <v>0.572</v>
       </c>
       <c r="AM6">
-        <v>0</v>
+        <v>0.572</v>
       </c>
       <c r="AN6">
-        <v>0</v>
+        <v>0.01704545454545454</v>
+      </c>
+      <c r="AO6">
+        <v>2.884615384615385</v>
       </c>
       <c r="AP6">
-        <v>-0.2531055900621118</v>
+        <v>-2.465909090909091</v>
+      </c>
+      <c r="AQ6">
+        <v>2.884615384615385</v>
       </c>
     </row>
     <row r="7">
@@ -1228,7 +1234,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>First Insurance Company (ASE:FINS)</t>
+          <t>Jordan Insurance Company (ASE:JOIN)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1237,46 +1243,43 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0649</v>
-      </c>
-      <c r="E7">
-        <v>0.06269999999999999</v>
+        <v>-0.00311</v>
       </c>
       <c r="G7">
-        <v>0.0872093023255814</v>
+        <v>0.04802527646129542</v>
       </c>
       <c r="H7">
-        <v>0.0872093023255814</v>
+        <v>0.04802527646129542</v>
       </c>
       <c r="I7">
-        <v>0.08581395348837209</v>
+        <v>0.07804107424960506</v>
       </c>
       <c r="J7">
-        <v>0.08051162790697675</v>
+        <v>0.04383128827717545</v>
       </c>
       <c r="K7">
-        <v>3.46</v>
+        <v>2.05</v>
       </c>
       <c r="L7">
-        <v>0.08046511627906977</v>
+        <v>0.03238546603475513</v>
       </c>
       <c r="M7">
-        <v>2.51</v>
+        <v>1.68</v>
       </c>
       <c r="N7">
-        <v>0.09507575757575758</v>
+        <v>0.03612903225806451</v>
       </c>
       <c r="O7">
-        <v>0.7254335260115606</v>
+        <v>0.8195121951219513</v>
       </c>
       <c r="P7">
-        <v>2.51</v>
+        <v>1.68</v>
       </c>
       <c r="Q7">
-        <v>0.09507575757575758</v>
+        <v>0.03612903225806451</v>
       </c>
       <c r="R7">
-        <v>0.7254335260115606</v>
+        <v>0.8195121951219513</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1285,55 +1288,55 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>15.8</v>
+        <v>36.1</v>
       </c>
       <c r="V7">
-        <v>0.5984848484848485</v>
+        <v>0.7763440860215054</v>
       </c>
       <c r="W7">
-        <v>0.07393162393162393</v>
+        <v>0.03445378151260504</v>
       </c>
       <c r="X7">
-        <v>0.1225413288938654</v>
+        <v>0.1212292600666038</v>
       </c>
       <c r="Y7">
-        <v>-0.04860970496224151</v>
+        <v>-0.08677547855399881</v>
       </c>
       <c r="Z7">
-        <v>1.08366935483871</v>
+        <v>1.793201133144476</v>
       </c>
       <c r="AA7">
-        <v>0.08724798387096774</v>
+        <v>0.07859831580581321</v>
       </c>
       <c r="AB7">
-        <v>0.1225413288938654</v>
+        <v>0.1139006631644434</v>
       </c>
       <c r="AC7">
-        <v>-0.0352933450228977</v>
+        <v>-0.03530234735863017</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>10.7</v>
       </c>
       <c r="AG7">
-        <v>-15.8</v>
+        <v>-25.4</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>0.187062937062937</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>0.1481994459833795</v>
       </c>
       <c r="AJ7">
-        <v>-1.490566037735849</v>
+        <v>-1.203791469194313</v>
       </c>
       <c r="AK7">
-        <v>-0.4922118380062306</v>
+        <v>-0.7036011080332412</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1342,10 +1345,10 @@
         <v>0</v>
       </c>
       <c r="AN7">
-        <v>0</v>
+        <v>2.053742802303263</v>
       </c>
       <c r="AP7">
-        <v>-3.657407407407407</v>
+        <v>-4.875239923224568</v>
       </c>
     </row>
     <row r="8">
@@ -1356,7 +1359,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Middle East Insurance Co. (ASE:MEIN)</t>
+          <t>Arabia Insurance Company - Jordan (ASE:AICJ)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1365,121 +1368,112 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0196</v>
+        <v>0.0325</v>
       </c>
       <c r="E8">
-        <v>0.225</v>
+        <v>0.113</v>
       </c>
       <c r="G8">
-        <v>0.1372492836676218</v>
+        <v>-0.01072202166064982</v>
       </c>
       <c r="H8">
-        <v>0.1372492836676218</v>
+        <v>-0.01072202166064982</v>
       </c>
       <c r="I8">
-        <v>0.1418338108882522</v>
+        <v>0.02523465703971119</v>
       </c>
       <c r="J8">
-        <v>0.1054083094555874</v>
+        <v>0.01836650879342894</v>
       </c>
       <c r="K8">
-        <v>3.27</v>
+        <v>0.476</v>
       </c>
       <c r="L8">
-        <v>0.09369627507163324</v>
+        <v>0.0171841155234657</v>
       </c>
       <c r="M8">
-        <v>1.547</v>
+        <v>-0</v>
       </c>
       <c r="N8">
-        <v>0.04789473684210527</v>
+        <v>-0</v>
       </c>
       <c r="O8">
-        <v>0.4730886850152906</v>
+        <v>-0</v>
       </c>
       <c r="P8">
-        <v>1.547</v>
+        <v>-0</v>
       </c>
       <c r="Q8">
-        <v>0.04789473684210527</v>
+        <v>-0</v>
       </c>
       <c r="R8">
-        <v>0.4730886850152906</v>
+        <v>-0</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
       <c r="U8">
-        <v>13</v>
+        <v>2.18</v>
       </c>
       <c r="V8">
-        <v>0.4024767801857586</v>
+        <v>0.2546728971962617</v>
       </c>
       <c r="W8">
-        <v>0.05726795096322242</v>
+        <v>0.03111111111111111</v>
       </c>
       <c r="X8">
-        <v>0.1226699223896282</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="Y8">
-        <v>-0.06540197142640576</v>
+        <v>-0.07730313867270798</v>
       </c>
       <c r="Z8">
-        <v>0.766645431979439</v>
+        <v>2.488769092542677</v>
       </c>
       <c r="AA8">
-        <v>0.08081079893680118</v>
+        <v>0.04570999942299924</v>
       </c>
       <c r="AB8">
-        <v>0.1226094447948534</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="AC8">
-        <v>-0.04179864585805221</v>
+        <v>-0.06270425036081984</v>
       </c>
       <c r="AD8">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="AE8">
         <v>0</v>
       </c>
       <c r="AF8">
-        <v>0.062</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>-12.938</v>
+        <v>-2.18</v>
       </c>
       <c r="AH8">
-        <v>0.001915827204746308</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>0.001005481495896987</v>
+        <v>0</v>
       </c>
       <c r="AJ8">
-        <v>-0.6682160933787834</v>
+        <v>-0.341692789968652</v>
       </c>
       <c r="AK8">
-        <v>-0.2658748099132794</v>
+        <v>-0.1600587371512482</v>
       </c>
       <c r="AL8">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AM8">
-        <v>0.006</v>
+        <v>0</v>
       </c>
       <c r="AN8">
-        <v>0.01067125645438899</v>
-      </c>
-      <c r="AO8">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="AP8">
-        <v>-2.22685025817556</v>
-      </c>
-      <c r="AQ8">
-        <v>825</v>
+        <v>-2.443946188340807</v>
       </c>
     </row>
     <row r="9">
@@ -1490,7 +1484,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Arab Assurers Insurance Company (ASE:ARAS)</t>
+          <t>Jordan International Insurance Company (ASE:JIJC)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1499,28 +1493,25 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.04019999999999999</v>
-      </c>
-      <c r="E9">
-        <v>-0.119</v>
+        <v>-0.0327</v>
       </c>
       <c r="G9">
-        <v>-0.1062176165803109</v>
+        <v>-0.261344537815126</v>
       </c>
       <c r="H9">
-        <v>-0.1062176165803109</v>
+        <v>-0.261344537815126</v>
       </c>
       <c r="I9">
-        <v>0.01694300518134715</v>
+        <v>-0.2487394957983193</v>
       </c>
       <c r="J9">
-        <v>0.01694300518134715</v>
+        <v>-0.2487394957983193</v>
       </c>
       <c r="K9">
-        <v>0.539</v>
+        <v>-3.29</v>
       </c>
       <c r="L9">
-        <v>0.02792746113989637</v>
+        <v>-0.2764705882352941</v>
       </c>
       <c r="M9">
         <v>-0</v>
@@ -1529,7 +1520,7 @@
         <v>-0</v>
       </c>
       <c r="O9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9">
         <v>-0</v>
@@ -1538,73 +1529,79 @@
         <v>-0</v>
       </c>
       <c r="R9">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="U9">
-        <v>2.7</v>
+        <v>7.46</v>
       </c>
       <c r="V9">
-        <v>1.298076923076923</v>
+        <v>0.5828125</v>
       </c>
       <c r="W9">
-        <v>0.0695483870967742</v>
+        <v>-0.1260536398467433</v>
       </c>
       <c r="X9">
-        <v>0.128403221916436</v>
+        <v>0.1158542727294648</v>
       </c>
       <c r="Y9">
-        <v>-0.05885483481966185</v>
+        <v>-0.241907912576208</v>
       </c>
       <c r="Z9">
-        <v>4.862685815066768</v>
+        <v>0.6552863436123348</v>
       </c>
       <c r="AA9">
-        <v>0.08238851095993954</v>
+        <v>-0.1629955947136564</v>
       </c>
       <c r="AB9">
-        <v>0.1246617900570834</v>
+        <v>0.1110711063505802</v>
       </c>
       <c r="AC9">
-        <v>-0.0422732790971439</v>
+        <v>-0.2740667010642366</v>
       </c>
       <c r="AD9">
-        <v>0.182</v>
+        <v>1.71</v>
       </c>
       <c r="AE9">
         <v>0</v>
       </c>
       <c r="AF9">
-        <v>0.182</v>
+        <v>1.71</v>
       </c>
       <c r="AG9">
-        <v>-2.518</v>
+        <v>-5.75</v>
       </c>
       <c r="AH9">
-        <v>0.08045977011494253</v>
+        <v>0.1178497587870434</v>
       </c>
       <c r="AI9">
-        <v>0.02202856451222464</v>
+        <v>0.06948394961397805</v>
       </c>
       <c r="AJ9">
-        <v>5.748858447488582</v>
+        <v>-0.8156028368794326</v>
       </c>
       <c r="AK9">
-        <v>-0.4527148507731033</v>
+        <v>-0.3352769679300292</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="AN9">
-        <v>0.4312796208530806</v>
+        <v>-0.6195652173913044</v>
+      </c>
+      <c r="AO9">
+        <v>-10.72463768115942</v>
       </c>
       <c r="AP9">
-        <v>-5.966824644549764</v>
+        <v>2.083333333333333</v>
+      </c>
+      <c r="AQ9">
+        <v>-10.72463768115942</v>
       </c>
     </row>
     <row r="10">
@@ -1615,7 +1612,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Jordan Insurance Company (ASE:JOIN)</t>
+          <t>Arab Jordanian Insurance Group (ASE:ARGR)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1624,454 +1621,112 @@
         </is>
       </c>
       <c r="D10">
-        <v>-0.0268</v>
+        <v>0.07769999999999999</v>
       </c>
       <c r="G10">
-        <v>0.06802218114602587</v>
+        <v>-0.1003676470588235</v>
       </c>
       <c r="H10">
-        <v>0.06802218114602587</v>
+        <v>-0.1003676470588235</v>
       </c>
       <c r="I10">
-        <v>0.04842883548983364</v>
+        <v>-0.05955882352941177</v>
       </c>
       <c r="J10">
-        <v>0.02421441774491682</v>
+        <v>-0.05955882352941177</v>
       </c>
       <c r="K10">
-        <v>0.376</v>
+        <v>-1.81</v>
       </c>
       <c r="L10">
-        <v>0.006950092421441774</v>
+        <v>-0.06654411764705882</v>
       </c>
       <c r="M10">
-        <v>3.39</v>
+        <v>-0</v>
       </c>
       <c r="N10">
-        <v>0.06075268817204302</v>
+        <v>-0</v>
       </c>
       <c r="O10">
-        <v>9.01595744680851</v>
+        <v>0</v>
       </c>
       <c r="P10">
-        <v>3.39</v>
+        <v>-0</v>
       </c>
       <c r="Q10">
-        <v>0.06075268817204302</v>
+        <v>-0</v>
       </c>
       <c r="R10">
-        <v>9.01595744680851</v>
+        <v>0</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
       <c r="U10">
-        <v>40.3</v>
+        <v>4.71</v>
       </c>
       <c r="V10">
-        <v>0.7222222222222222</v>
+        <v>0.4361111111111111</v>
       </c>
       <c r="W10">
-        <v>0.005363766048502141</v>
+        <v>-0.1691588785046729</v>
       </c>
       <c r="X10">
-        <v>0.1418708686098688</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="Y10">
-        <v>-0.1365071025613667</v>
+        <v>-0.277573128288492</v>
       </c>
       <c r="Z10">
-        <v>0.6006439435994227</v>
+        <v>23.85964912280704</v>
       </c>
       <c r="AA10">
-        <v>0.01454424336627068</v>
+        <v>-1.421052631578949</v>
       </c>
       <c r="AB10">
-        <v>0.1305027235914999</v>
+        <v>0.1084142497838191</v>
       </c>
       <c r="AC10">
-        <v>-0.1159584802252292</v>
+        <v>-1.529466881362768</v>
       </c>
       <c r="AD10">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="AE10">
         <v>0</v>
       </c>
       <c r="AF10">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="AG10">
-        <v>-24.2</v>
+        <v>-4.71</v>
       </c>
       <c r="AH10">
-        <v>0.2239221140472879</v>
+        <v>0</v>
       </c>
       <c r="AI10">
-        <v>0.212962962962963</v>
+        <v>0</v>
       </c>
       <c r="AJ10">
-        <v>-0.7658227848101264</v>
+        <v>-0.7733990147783251</v>
       </c>
       <c r="AK10">
-        <v>-0.6855524079320111</v>
+        <v>-2.030172413793103</v>
       </c>
       <c r="AL10">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AM10">
-        <v>2.09</v>
+        <v>-0.101</v>
       </c>
       <c r="AN10">
-        <v>5.127388535031847</v>
-      </c>
-      <c r="AO10">
-        <v>1.253588516746412</v>
+        <v>-0</v>
       </c>
       <c r="AP10">
-        <v>-7.70700636942675</v>
+        <v>3.437956204379562</v>
       </c>
       <c r="AQ10">
-        <v>1.253588516746412</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Arab Union International Insurance PLC (ASE:AIUI)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>-0</v>
-      </c>
-      <c r="N11">
-        <v>-0</v>
-      </c>
-      <c r="P11">
-        <v>-0</v>
-      </c>
-      <c r="Q11">
-        <v>-0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>1.24</v>
-      </c>
-      <c r="V11">
-        <v>0.2995169082125604</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0.1225413288938654</v>
-      </c>
-      <c r="Y11">
-        <v>-0.1225413288938654</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0.1225413288938654</v>
-      </c>
-      <c r="AC11">
-        <v>-0.1225413288938654</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>-1.24</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>-0.4275862068965518</v>
-      </c>
-      <c r="AK11">
-        <v>-0.3583815028901734</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Arabia Insurance Company - Jordan (ASE:AICJ)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>0.0285</v>
-      </c>
-      <c r="G12">
-        <v>-0.02698347107438017</v>
-      </c>
-      <c r="H12">
-        <v>-0.02698347107438017</v>
-      </c>
-      <c r="I12">
-        <v>-0.006115702479338843</v>
-      </c>
-      <c r="J12">
-        <v>-0.006115702479338843</v>
-      </c>
-      <c r="K12">
-        <v>-0.154</v>
-      </c>
-      <c r="L12">
-        <v>-0.006363636363636364</v>
-      </c>
-      <c r="M12">
-        <v>-0</v>
-      </c>
-      <c r="N12">
-        <v>-0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>-0</v>
-      </c>
-      <c r="Q12">
-        <v>-0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="U12">
-        <v>4.17</v>
-      </c>
-      <c r="V12">
-        <v>0.5366795366795367</v>
-      </c>
-      <c r="W12">
-        <v>-0.01</v>
-      </c>
-      <c r="X12">
-        <v>0.1225413288938654</v>
-      </c>
-      <c r="Y12">
-        <v>-0.1325413288938654</v>
-      </c>
-      <c r="Z12">
-        <v>2.052586938083121</v>
-      </c>
-      <c r="AA12">
-        <v>-0.01255301102629347</v>
-      </c>
-      <c r="AB12">
-        <v>0.1225413288938654</v>
-      </c>
-      <c r="AC12">
-        <v>-0.1350943399201589</v>
-      </c>
-      <c r="AD12">
-        <v>0</v>
-      </c>
-      <c r="AE12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>0</v>
-      </c>
-      <c r="AG12">
-        <v>-4.17</v>
-      </c>
-      <c r="AH12">
-        <v>0</v>
-      </c>
-      <c r="AI12">
-        <v>0</v>
-      </c>
-      <c r="AJ12">
-        <v>-1.158333333333333</v>
-      </c>
-      <c r="AK12">
-        <v>-0.3746630727762803</v>
-      </c>
-      <c r="AL12">
-        <v>0</v>
-      </c>
-      <c r="AM12">
-        <v>0</v>
-      </c>
-      <c r="AN12">
-        <v>0</v>
-      </c>
-      <c r="AP12">
-        <v>-85.10204081632652</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Jordan</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Jordan International Insurance Company (ASE:JIJC)</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Insurance (General)</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>0.0254</v>
-      </c>
-      <c r="G13">
-        <v>-0.004875</v>
-      </c>
-      <c r="H13">
-        <v>-0.004875</v>
-      </c>
-      <c r="I13">
-        <v>-0.08749999999999999</v>
-      </c>
-      <c r="J13">
-        <v>-0.08749999999999999</v>
-      </c>
-      <c r="K13">
-        <v>-1.64</v>
-      </c>
-      <c r="L13">
-        <v>-0.1025</v>
-      </c>
-      <c r="M13">
-        <v>-0</v>
-      </c>
-      <c r="N13">
-        <v>-0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>-0</v>
-      </c>
-      <c r="Q13">
-        <v>-0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>9.02</v>
-      </c>
-      <c r="V13">
-        <v>1.176010430247718</v>
-      </c>
-      <c r="W13">
-        <v>-0.05655172413793103</v>
-      </c>
-      <c r="X13">
-        <v>0.1319745111838654</v>
-      </c>
-      <c r="Y13">
-        <v>-0.1885262353217964</v>
-      </c>
-      <c r="Z13">
-        <v>1</v>
-      </c>
-      <c r="AA13">
-        <v>-0.08749999999999999</v>
-      </c>
-      <c r="AB13">
-        <v>0.1257942028676771</v>
-      </c>
-      <c r="AC13">
-        <v>-0.2132942028676771</v>
-      </c>
-      <c r="AD13">
-        <v>1.08</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>1.08</v>
-      </c>
-      <c r="AG13">
-        <v>-7.94</v>
-      </c>
-      <c r="AH13">
-        <v>0.1234285714285714</v>
-      </c>
-      <c r="AI13">
-        <v>0.03805496828752643</v>
-      </c>
-      <c r="AJ13">
-        <v>29.40740740740745</v>
-      </c>
-      <c r="AK13">
-        <v>-0.4101239669421488</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>-0.870967741935484</v>
-      </c>
-      <c r="AP13">
-        <v>6.403225806451613</v>
+        <v>16.03960396039604</v>
       </c>
     </row>
   </sheetData>
